--- a/backend/MODULE_2_FINAL_OPPORTUNITY_AUDIT.xlsx
+++ b/backend/MODULE_2_FINAL_OPPORTUNITY_AUDIT.xlsx
@@ -493,10 +493,10 @@
         <v>4931</v>
       </c>
       <c r="C6">
-        <v>323.27</v>
+        <v>173.12</v>
       </c>
       <c r="D6">
-        <v>243.75</v>
+        <v>93.6</v>
       </c>
       <c r="E6" t="str">
         <v>PASS</v>
@@ -532,7 +532,7 @@
         <v>Gross Identified Opportunity</v>
       </c>
       <c r="B2">
-        <v>323.27</v>
+        <v>173.12</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -574,7 +574,7 @@
         <v>Net Defensible Opportunity</v>
       </c>
       <c r="B5">
-        <v>243.75</v>
+        <v>93.6</v>
       </c>
       <c r="C5">
         <v>0</v>
